--- a/data/out/test0/seikyuusyo202505_Python版_1pt.xlsx
+++ b/data/out/test0/seikyuusyo202505_Python版_1pt.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +57,32 @@
       <sz val="8.6"/>
     </font>
     <font>
+      <name val="MS Mincho"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="6.5"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="7.9"/>
+    </font>
+    <font>
+      <name val="MS PGothic"/>
+      <sz val="7"/>
+    </font>
+    <font>
       <name val="MS Gothic"/>
       <sz val="7"/>
+    </font>
+    <font>
+      <name val="MS PMincho"/>
+      <sz val="5.1"/>
+    </font>
+    <font>
+      <name val="MS PMincho"/>
+      <sz val="7.6"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,34 +199,70 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -688,7 +748,7 @@
       <c r="BH6" s="2"/>
       <c r="BI6" s="2"/>
       <c r="BJ6" s="2"/>
-      <c r="BK6" s="12" t="inlineStr">
+      <c r="BK6" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -707,40 +767,40 @@
       <c r="BW6" s="3"/>
     </row>
     <row r="7">
-      <c r="AZ7" s="13" t="inlineStr">
+      <c r="AZ7" s="14" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="BF7" s="14" t="inlineStr">
+      <c r="BF7" s="15" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="BW7" s="15"/>
+      <c r="BW7" s="16"/>
     </row>
     <row r="8">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="AZ8" s="13" t="inlineStr">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="AZ8" s="14" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="BW8" s="15"/>
+      <c r="BW8" s="16"/>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
@@ -748,17 +808,17 @@
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AZ9" s="13" t="inlineStr">
+      <c r="AZ9" s="14" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="BV9" s="14" t="inlineStr">
+      <c r="BV9" s="21" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="BW9" s="15"/>
+      <c r="BW9" s="16"/>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
@@ -781,23 +841,23 @@
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AZ10" s="20"/>
-      <c r="BG10" s="14" t="inlineStr">
+      <c r="AZ10" s="22"/>
+      <c r="BG10" s="9" t="inlineStr">
         <is>
           <t>電話FAX</t>
         </is>
       </c>
-      <c r="BM10" s="14" t="inlineStr">
+      <c r="BM10" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="BR10" s="14" t="inlineStr">
+      <c r="BR10" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="BW10" s="15"/>
+      <c r="BW10" s="16"/>
     </row>
     <row r="11">
       <c r="G11" s="9" t="inlineStr">
@@ -810,12 +870,12 @@
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AZ11" s="13" t="inlineStr">
+      <c r="AZ11" s="14" t="inlineStr">
         <is>
           <t>登録番号Ｔ</t>
         </is>
       </c>
-      <c r="BW11" s="15"/>
+      <c r="BW11" s="16"/>
     </row>
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
@@ -823,7 +883,7 @@
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="AZ12" s="21" t="inlineStr">
+      <c r="AZ12" s="23" t="inlineStr">
         <is>
           <t>振込先情報</t>
         </is>
@@ -837,7 +897,7 @@
       <c r="BG12" s="6"/>
       <c r="BH12" s="6"/>
       <c r="BI12" s="6"/>
-      <c r="BJ12" s="22" t="inlineStr">
+      <c r="BJ12" s="24" t="inlineStr">
         <is>
           <t>銀行預金</t>
         </is>
@@ -846,7 +906,7 @@
       <c r="BL12" s="6"/>
       <c r="BM12" s="6"/>
       <c r="BN12" s="6"/>
-      <c r="BO12" s="22" t="inlineStr">
+      <c r="BO12" s="25" t="inlineStr">
         <is>
           <t>口座番号：支店</t>
         </is>
@@ -861,7 +921,7 @@
       <c r="BW12" s="7"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
@@ -869,13 +929,13 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="18"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="19"/>
       <c r="M13" s="1"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -922,52 +982,52 @@
       <c r="BD13" s="2"/>
       <c r="BE13" s="2"/>
       <c r="BF13" s="3"/>
-      <c r="BG13" s="16" t="inlineStr">
+      <c r="BG13" s="17" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：</t>
         </is>
       </c>
-      <c r="BH13" s="17"/>
-      <c r="BI13" s="17"/>
-      <c r="BJ13" s="17"/>
-      <c r="BK13" s="17"/>
-      <c r="BL13" s="17"/>
-      <c r="BM13" s="17"/>
-      <c r="BN13" s="17"/>
-      <c r="BO13" s="17"/>
-      <c r="BP13" s="17"/>
-      <c r="BQ13" s="17"/>
-      <c r="BR13" s="17"/>
-      <c r="BS13" s="17"/>
-      <c r="BT13" s="18"/>
+      <c r="BH13" s="18"/>
+      <c r="BI13" s="18"/>
+      <c r="BJ13" s="18"/>
+      <c r="BK13" s="18"/>
+      <c r="BL13" s="18"/>
+      <c r="BM13" s="18"/>
+      <c r="BN13" s="18"/>
+      <c r="BO13" s="18"/>
+      <c r="BP13" s="18"/>
+      <c r="BQ13" s="18"/>
+      <c r="BR13" s="18"/>
+      <c r="BS13" s="18"/>
+      <c r="BT13" s="19"/>
       <c r="BU13" s="1"/>
       <c r="BV13" s="2"/>
       <c r="BW13" s="2"/>
       <c r="BX13" s="3"/>
     </row>
     <row r="14">
-      <c r="B14" s="24"/>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="B14" s="27"/>
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="7"/>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
-      <c r="N14" s="22" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="28" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="7"/>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="27"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -977,7 +1037,7 @@
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
-      <c r="AA14" s="22" t="inlineStr">
+      <c r="AA14" s="28" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
@@ -996,15 +1056,15 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
       <c r="AO14" s="7"/>
-      <c r="AP14" s="21" t="inlineStr">
+      <c r="AP14" s="30" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
       <c r="AQ14" s="6"/>
       <c r="AR14" s="7"/>
-      <c r="AS14" s="24"/>
-      <c r="AT14" s="22" t="inlineStr">
+      <c r="AS14" s="27"/>
+      <c r="AT14" s="28" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
@@ -1014,7 +1074,7 @@
       <c r="AW14" s="6"/>
       <c r="AX14" s="6"/>
       <c r="AY14" s="7"/>
-      <c r="AZ14" s="21" t="inlineStr">
+      <c r="AZ14" s="31" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
@@ -1025,25 +1085,25 @@
       <c r="BD14" s="6"/>
       <c r="BE14" s="6"/>
       <c r="BF14" s="7"/>
-      <c r="BG14" s="19"/>
-      <c r="BH14" s="17"/>
-      <c r="BI14" s="17"/>
-      <c r="BJ14" s="17"/>
-      <c r="BK14" s="17"/>
-      <c r="BL14" s="25" t="inlineStr">
+      <c r="BG14" s="20"/>
+      <c r="BH14" s="18"/>
+      <c r="BI14" s="18"/>
+      <c r="BJ14" s="18"/>
+      <c r="BK14" s="18"/>
+      <c r="BL14" s="32" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="BM14" s="17"/>
-      <c r="BN14" s="17"/>
-      <c r="BO14" s="17"/>
-      <c r="BP14" s="18"/>
-      <c r="BQ14" s="19"/>
-      <c r="BR14" s="17"/>
-      <c r="BS14" s="17"/>
-      <c r="BT14" s="18"/>
-      <c r="BU14" s="21" t="inlineStr">
+      <c r="BM14" s="18"/>
+      <c r="BN14" s="18"/>
+      <c r="BO14" s="18"/>
+      <c r="BP14" s="19"/>
+      <c r="BQ14" s="20"/>
+      <c r="BR14" s="18"/>
+      <c r="BS14" s="18"/>
+      <c r="BT14" s="19"/>
+      <c r="BU14" s="33" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
@@ -1053,253 +1113,253 @@
       <c r="BX14" s="7"/>
     </row>
     <row r="15">
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="17"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="17"/>
-      <c r="AK15" s="17"/>
-      <c r="AL15" s="17"/>
-      <c r="AM15" s="17"/>
-      <c r="AN15" s="17"/>
-      <c r="AO15" s="18"/>
-      <c r="AP15" s="19"/>
-      <c r="AQ15" s="17"/>
-      <c r="AR15" s="18"/>
-      <c r="AS15" s="19"/>
-      <c r="AT15" s="25" t="inlineStr">
+      <c r="B15" s="20"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="18"/>
+      <c r="Z15" s="18"/>
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="18"/>
+      <c r="AG15" s="18"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="18"/>
+      <c r="AN15" s="18"/>
+      <c r="AO15" s="19"/>
+      <c r="AP15" s="20"/>
+      <c r="AQ15" s="18"/>
+      <c r="AR15" s="19"/>
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AU15" s="17"/>
-      <c r="AV15" s="17"/>
-      <c r="AW15" s="17"/>
-      <c r="AX15" s="17"/>
-      <c r="AY15" s="18"/>
-      <c r="AZ15" s="19"/>
-      <c r="BA15" s="25" t="inlineStr">
+      <c r="AU15" s="18"/>
+      <c r="AV15" s="18"/>
+      <c r="AW15" s="18"/>
+      <c r="AX15" s="18"/>
+      <c r="AY15" s="19"/>
+      <c r="AZ15" s="20"/>
+      <c r="BA15" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BB15" s="17"/>
-      <c r="BC15" s="17"/>
-      <c r="BD15" s="17"/>
-      <c r="BE15" s="17"/>
-      <c r="BF15" s="18"/>
-      <c r="BG15" s="14" t="inlineStr">
+      <c r="BB15" s="18"/>
+      <c r="BC15" s="18"/>
+      <c r="BD15" s="18"/>
+      <c r="BE15" s="18"/>
+      <c r="BF15" s="19"/>
+      <c r="BG15" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BJ15" s="14" t="inlineStr">
+      <c r="BJ15" s="10" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BQ15" s="14" t="inlineStr">
+      <c r="BQ15" s="35" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="BR15" s="14" t="inlineStr">
+      <c r="BR15" s="10" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="BU15" s="19"/>
-      <c r="BV15" s="17"/>
-      <c r="BW15" s="17"/>
-      <c r="BX15" s="18"/>
+      <c r="BU15" s="20"/>
+      <c r="BV15" s="18"/>
+      <c r="BW15" s="18"/>
+      <c r="BX15" s="19"/>
     </row>
     <row r="16">
-      <c r="BG16" s="19"/>
-      <c r="BH16" s="17"/>
-      <c r="BI16" s="17"/>
-      <c r="BJ16" s="17"/>
-      <c r="BK16" s="17"/>
-      <c r="BL16" s="17"/>
-      <c r="BM16" s="17"/>
-      <c r="BN16" s="17"/>
-      <c r="BO16" s="17"/>
-      <c r="BP16" s="18"/>
-      <c r="BQ16" s="19"/>
-      <c r="BR16" s="17"/>
-      <c r="BS16" s="17"/>
-      <c r="BT16" s="18"/>
+      <c r="BG16" s="20"/>
+      <c r="BH16" s="18"/>
+      <c r="BI16" s="18"/>
+      <c r="BJ16" s="18"/>
+      <c r="BK16" s="18"/>
+      <c r="BL16" s="18"/>
+      <c r="BM16" s="18"/>
+      <c r="BN16" s="18"/>
+      <c r="BO16" s="18"/>
+      <c r="BP16" s="19"/>
+      <c r="BQ16" s="20"/>
+      <c r="BR16" s="18"/>
+      <c r="BS16" s="18"/>
+      <c r="BT16" s="19"/>
     </row>
     <row r="17">
-      <c r="B17" s="19"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="17"/>
-      <c r="AK17" s="17"/>
-      <c r="AL17" s="17"/>
-      <c r="AM17" s="17"/>
-      <c r="AN17" s="17"/>
-      <c r="AO17" s="18"/>
-      <c r="AP17" s="19"/>
-      <c r="AQ17" s="17"/>
-      <c r="AR17" s="18"/>
-      <c r="AS17" s="19"/>
-      <c r="AT17" s="17"/>
-      <c r="AU17" s="17"/>
-      <c r="AV17" s="17"/>
-      <c r="AW17" s="17"/>
-      <c r="AX17" s="17"/>
-      <c r="AY17" s="18"/>
-      <c r="AZ17" s="19"/>
-      <c r="BA17" s="17"/>
-      <c r="BB17" s="17"/>
-      <c r="BC17" s="17"/>
-      <c r="BD17" s="17"/>
-      <c r="BE17" s="17"/>
-      <c r="BF17" s="18"/>
-      <c r="BU17" s="19"/>
-      <c r="BV17" s="17"/>
-      <c r="BW17" s="17"/>
-      <c r="BX17" s="18"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="18"/>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="18"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="18"/>
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="18"/>
+      <c r="AN17" s="18"/>
+      <c r="AO17" s="19"/>
+      <c r="AP17" s="20"/>
+      <c r="AQ17" s="18"/>
+      <c r="AR17" s="19"/>
+      <c r="AS17" s="20"/>
+      <c r="AT17" s="18"/>
+      <c r="AU17" s="18"/>
+      <c r="AV17" s="18"/>
+      <c r="AW17" s="18"/>
+      <c r="AX17" s="18"/>
+      <c r="AY17" s="19"/>
+      <c r="AZ17" s="20"/>
+      <c r="BA17" s="18"/>
+      <c r="BB17" s="18"/>
+      <c r="BC17" s="18"/>
+      <c r="BD17" s="18"/>
+      <c r="BE17" s="18"/>
+      <c r="BF17" s="19"/>
+      <c r="BU17" s="20"/>
+      <c r="BV17" s="18"/>
+      <c r="BW17" s="18"/>
+      <c r="BX17" s="19"/>
     </row>
     <row r="18">
-      <c r="BG18" s="19"/>
-      <c r="BH18" s="17"/>
-      <c r="BI18" s="17"/>
-      <c r="BJ18" s="17"/>
-      <c r="BK18" s="17"/>
-      <c r="BL18" s="17"/>
-      <c r="BM18" s="17"/>
-      <c r="BN18" s="17"/>
-      <c r="BO18" s="17"/>
-      <c r="BP18" s="18"/>
-      <c r="BQ18" s="19"/>
-      <c r="BR18" s="17"/>
-      <c r="BS18" s="17"/>
-      <c r="BT18" s="18"/>
+      <c r="BG18" s="20"/>
+      <c r="BH18" s="18"/>
+      <c r="BI18" s="18"/>
+      <c r="BJ18" s="18"/>
+      <c r="BK18" s="18"/>
+      <c r="BL18" s="18"/>
+      <c r="BM18" s="18"/>
+      <c r="BN18" s="18"/>
+      <c r="BO18" s="18"/>
+      <c r="BP18" s="19"/>
+      <c r="BQ18" s="20"/>
+      <c r="BR18" s="18"/>
+      <c r="BS18" s="18"/>
+      <c r="BT18" s="19"/>
     </row>
     <row r="19">
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="17"/>
-      <c r="AH19" s="17"/>
-      <c r="AI19" s="17"/>
-      <c r="AJ19" s="17"/>
-      <c r="AK19" s="17"/>
-      <c r="AL19" s="17"/>
-      <c r="AM19" s="17"/>
-      <c r="AN19" s="17"/>
-      <c r="AO19" s="18"/>
-      <c r="AP19" s="19"/>
-      <c r="AQ19" s="17"/>
-      <c r="AR19" s="18"/>
-      <c r="AS19" s="19"/>
-      <c r="AT19" s="17"/>
-      <c r="AU19" s="17"/>
-      <c r="AV19" s="17"/>
-      <c r="AW19" s="17"/>
-      <c r="AX19" s="17"/>
-      <c r="AY19" s="18"/>
-      <c r="AZ19" s="19"/>
-      <c r="BA19" s="17"/>
-      <c r="BB19" s="17"/>
-      <c r="BC19" s="17"/>
-      <c r="BD19" s="17"/>
-      <c r="BE19" s="17"/>
-      <c r="BF19" s="18"/>
-      <c r="BU19" s="19"/>
-      <c r="BV19" s="17"/>
-      <c r="BW19" s="17"/>
-      <c r="BX19" s="18"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
+      <c r="AD19" s="18"/>
+      <c r="AE19" s="18"/>
+      <c r="AF19" s="18"/>
+      <c r="AG19" s="18"/>
+      <c r="AH19" s="18"/>
+      <c r="AI19" s="18"/>
+      <c r="AJ19" s="18"/>
+      <c r="AK19" s="18"/>
+      <c r="AL19" s="18"/>
+      <c r="AM19" s="18"/>
+      <c r="AN19" s="18"/>
+      <c r="AO19" s="19"/>
+      <c r="AP19" s="20"/>
+      <c r="AQ19" s="18"/>
+      <c r="AR19" s="19"/>
+      <c r="AS19" s="20"/>
+      <c r="AT19" s="18"/>
+      <c r="AU19" s="18"/>
+      <c r="AV19" s="18"/>
+      <c r="AW19" s="18"/>
+      <c r="AX19" s="18"/>
+      <c r="AY19" s="19"/>
+      <c r="AZ19" s="20"/>
+      <c r="BA19" s="18"/>
+      <c r="BB19" s="18"/>
+      <c r="BC19" s="18"/>
+      <c r="BD19" s="18"/>
+      <c r="BE19" s="18"/>
+      <c r="BF19" s="19"/>
+      <c r="BU19" s="20"/>
+      <c r="BV19" s="18"/>
+      <c r="BW19" s="18"/>
+      <c r="BX19" s="19"/>
     </row>
     <row r="20">
       <c r="B20" s="1"/>
@@ -1372,22 +1432,22 @@
       <c r="BX20" s="3"/>
     </row>
     <row r="21">
-      <c r="B21" s="24"/>
+      <c r="B21" s="27"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="24"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="27"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="24"/>
+      <c r="Q21" s="27"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
       <c r="T21" s="6"/>
@@ -1412,24 +1472,24 @@
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
       <c r="AO21" s="7"/>
-      <c r="AP21" s="24"/>
+      <c r="AP21" s="27"/>
       <c r="AQ21" s="6"/>
       <c r="AR21" s="7"/>
-      <c r="AS21" s="24"/>
+      <c r="AS21" s="27"/>
       <c r="AT21" s="6"/>
       <c r="AU21" s="6"/>
       <c r="AV21" s="6"/>
       <c r="AW21" s="6"/>
       <c r="AX21" s="6"/>
       <c r="AY21" s="7"/>
-      <c r="AZ21" s="24"/>
+      <c r="AZ21" s="27"/>
       <c r="BA21" s="6"/>
       <c r="BB21" s="6"/>
       <c r="BC21" s="6"/>
       <c r="BD21" s="6"/>
       <c r="BE21" s="6"/>
       <c r="BF21" s="7"/>
-      <c r="BG21" s="24"/>
+      <c r="BG21" s="27"/>
       <c r="BH21" s="6"/>
       <c r="BI21" s="6"/>
       <c r="BJ21" s="6"/>
@@ -1439,332 +1499,332 @@
       <c r="BN21" s="6"/>
       <c r="BO21" s="6"/>
       <c r="BP21" s="7"/>
-      <c r="BQ21" s="24"/>
+      <c r="BQ21" s="27"/>
       <c r="BR21" s="6"/>
       <c r="BS21" s="6"/>
       <c r="BT21" s="7"/>
-      <c r="BU21" s="24"/>
+      <c r="BU21" s="27"/>
       <c r="BV21" s="6"/>
       <c r="BW21" s="6"/>
       <c r="BX21" s="7"/>
     </row>
     <row r="22">
-      <c r="B22" s="19"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="17"/>
-      <c r="AF22" s="17"/>
-      <c r="AG22" s="17"/>
-      <c r="AH22" s="17"/>
-      <c r="AI22" s="17"/>
-      <c r="AJ22" s="17"/>
-      <c r="AK22" s="17"/>
-      <c r="AL22" s="17"/>
-      <c r="AM22" s="17"/>
-      <c r="AN22" s="17"/>
-      <c r="AO22" s="17"/>
-      <c r="AP22" s="17"/>
-      <c r="AQ22" s="17"/>
-      <c r="AR22" s="17"/>
-      <c r="AS22" s="17"/>
-      <c r="AT22" s="17"/>
-      <c r="AU22" s="17"/>
-      <c r="AV22" s="17"/>
-      <c r="AW22" s="17"/>
-      <c r="AX22" s="17"/>
-      <c r="AY22" s="18"/>
-      <c r="AZ22" s="19"/>
-      <c r="BA22" s="25" t="inlineStr">
+      <c r="B22" s="20"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
+      <c r="AF22" s="18"/>
+      <c r="AG22" s="18"/>
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="18"/>
+      <c r="AJ22" s="18"/>
+      <c r="AK22" s="18"/>
+      <c r="AL22" s="18"/>
+      <c r="AM22" s="18"/>
+      <c r="AN22" s="18"/>
+      <c r="AO22" s="18"/>
+      <c r="AP22" s="18"/>
+      <c r="AQ22" s="18"/>
+      <c r="AR22" s="18"/>
+      <c r="AS22" s="18"/>
+      <c r="AT22" s="18"/>
+      <c r="AU22" s="18"/>
+      <c r="AV22" s="18"/>
+      <c r="AW22" s="18"/>
+      <c r="AX22" s="18"/>
+      <c r="AY22" s="19"/>
+      <c r="AZ22" s="20"/>
+      <c r="BA22" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BB22" s="17"/>
-      <c r="BC22" s="17"/>
-      <c r="BD22" s="17"/>
-      <c r="BE22" s="17"/>
-      <c r="BF22" s="18"/>
-      <c r="BG22" s="19"/>
-      <c r="BH22" s="25" t="inlineStr">
+      <c r="BB22" s="18"/>
+      <c r="BC22" s="18"/>
+      <c r="BD22" s="18"/>
+      <c r="BE22" s="18"/>
+      <c r="BF22" s="19"/>
+      <c r="BG22" s="20"/>
+      <c r="BH22" s="34" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="BI22" s="17"/>
-      <c r="BJ22" s="17"/>
-      <c r="BK22" s="17"/>
-      <c r="BL22" s="18"/>
-      <c r="BM22" s="19"/>
-      <c r="BN22" s="17"/>
-      <c r="BO22" s="25" t="inlineStr">
+      <c r="BI22" s="18"/>
+      <c r="BJ22" s="18"/>
+      <c r="BK22" s="18"/>
+      <c r="BL22" s="19"/>
+      <c r="BM22" s="20"/>
+      <c r="BN22" s="18"/>
+      <c r="BO22" s="34" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="BP22" s="17"/>
-      <c r="BQ22" s="17"/>
-      <c r="BR22" s="17"/>
-      <c r="BS22" s="17"/>
-      <c r="BT22" s="18"/>
-      <c r="BU22" s="19"/>
-      <c r="BV22" s="17"/>
-      <c r="BW22" s="17"/>
-      <c r="BX22" s="18"/>
+      <c r="BP22" s="18"/>
+      <c r="BQ22" s="18"/>
+      <c r="BR22" s="18"/>
+      <c r="BS22" s="18"/>
+      <c r="BT22" s="19"/>
+      <c r="BU22" s="20"/>
+      <c r="BV22" s="18"/>
+      <c r="BW22" s="18"/>
+      <c r="BX22" s="19"/>
     </row>
     <row r="23">
-      <c r="AR23" s="14" t="inlineStr">
+      <c r="AR23" s="10" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="17"/>
-      <c r="AK24" s="17"/>
-      <c r="AL24" s="17"/>
-      <c r="AM24" s="17"/>
-      <c r="AN24" s="17"/>
-      <c r="AO24" s="17"/>
-      <c r="AP24" s="17"/>
-      <c r="AQ24" s="17"/>
-      <c r="AR24" s="17"/>
-      <c r="AS24" s="17"/>
-      <c r="AT24" s="17"/>
-      <c r="AU24" s="17"/>
-      <c r="AV24" s="25" t="inlineStr">
+      <c r="B24" s="20"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="18"/>
+      <c r="AL24" s="18"/>
+      <c r="AM24" s="18"/>
+      <c r="AN24" s="18"/>
+      <c r="AO24" s="18"/>
+      <c r="AP24" s="18"/>
+      <c r="AQ24" s="18"/>
+      <c r="AR24" s="18"/>
+      <c r="AS24" s="18"/>
+      <c r="AT24" s="18"/>
+      <c r="AU24" s="18"/>
+      <c r="AV24" s="34" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AW24" s="17"/>
-      <c r="AX24" s="17"/>
-      <c r="AY24" s="18"/>
-      <c r="AZ24" s="19"/>
-      <c r="BA24" s="17"/>
-      <c r="BB24" s="17"/>
-      <c r="BC24" s="17"/>
-      <c r="BD24" s="17"/>
-      <c r="BE24" s="17"/>
-      <c r="BF24" s="18"/>
-      <c r="BG24" s="19"/>
-      <c r="BH24" s="17"/>
-      <c r="BI24" s="17"/>
-      <c r="BJ24" s="17"/>
-      <c r="BK24" s="17"/>
-      <c r="BL24" s="18"/>
-      <c r="BM24" s="19"/>
-      <c r="BN24" s="17"/>
-      <c r="BO24" s="17"/>
-      <c r="BP24" s="17"/>
-      <c r="BQ24" s="17"/>
-      <c r="BR24" s="17"/>
-      <c r="BS24" s="17"/>
-      <c r="BT24" s="18"/>
-      <c r="BU24" s="19"/>
-      <c r="BV24" s="17"/>
-      <c r="BW24" s="17"/>
-      <c r="BX24" s="18"/>
+      <c r="AW24" s="18"/>
+      <c r="AX24" s="18"/>
+      <c r="AY24" s="19"/>
+      <c r="AZ24" s="20"/>
+      <c r="BA24" s="18"/>
+      <c r="BB24" s="18"/>
+      <c r="BC24" s="18"/>
+      <c r="BD24" s="18"/>
+      <c r="BE24" s="18"/>
+      <c r="BF24" s="19"/>
+      <c r="BG24" s="20"/>
+      <c r="BH24" s="18"/>
+      <c r="BI24" s="18"/>
+      <c r="BJ24" s="18"/>
+      <c r="BK24" s="18"/>
+      <c r="BL24" s="19"/>
+      <c r="BM24" s="20"/>
+      <c r="BN24" s="18"/>
+      <c r="BO24" s="18"/>
+      <c r="BP24" s="18"/>
+      <c r="BQ24" s="18"/>
+      <c r="BR24" s="18"/>
+      <c r="BS24" s="18"/>
+      <c r="BT24" s="19"/>
+      <c r="BU24" s="20"/>
+      <c r="BV24" s="18"/>
+      <c r="BW24" s="18"/>
+      <c r="BX24" s="19"/>
     </row>
     <row r="25">
-      <c r="AU25" s="14" t="inlineStr">
+      <c r="AU25" s="10" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="17"/>
-      <c r="AD26" s="17"/>
-      <c r="AE26" s="17"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="17"/>
-      <c r="AH26" s="17"/>
-      <c r="AI26" s="17"/>
-      <c r="AJ26" s="17"/>
-      <c r="AK26" s="17"/>
-      <c r="AL26" s="17"/>
-      <c r="AM26" s="17"/>
-      <c r="AN26" s="17"/>
-      <c r="AO26" s="17"/>
-      <c r="AP26" s="17"/>
-      <c r="AQ26" s="17"/>
-      <c r="AR26" s="17"/>
-      <c r="AS26" s="17"/>
-      <c r="AT26" s="17"/>
-      <c r="AU26" s="17"/>
-      <c r="AV26" s="17"/>
-      <c r="AW26" s="25" t="inlineStr">
+      <c r="B26" s="20"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="18"/>
+      <c r="AN26" s="18"/>
+      <c r="AO26" s="18"/>
+      <c r="AP26" s="18"/>
+      <c r="AQ26" s="18"/>
+      <c r="AR26" s="18"/>
+      <c r="AS26" s="18"/>
+      <c r="AT26" s="18"/>
+      <c r="AU26" s="18"/>
+      <c r="AV26" s="18"/>
+      <c r="AW26" s="34" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AX26" s="17"/>
-      <c r="AY26" s="18"/>
-      <c r="AZ26" s="19"/>
-      <c r="BA26" s="17"/>
-      <c r="BB26" s="17"/>
-      <c r="BC26" s="17"/>
-      <c r="BD26" s="17"/>
-      <c r="BE26" s="17"/>
-      <c r="BF26" s="18"/>
-      <c r="BG26" s="19"/>
-      <c r="BH26" s="17"/>
-      <c r="BI26" s="17"/>
-      <c r="BJ26" s="17"/>
-      <c r="BK26" s="17"/>
-      <c r="BL26" s="18"/>
-      <c r="BM26" s="19"/>
-      <c r="BN26" s="17"/>
-      <c r="BO26" s="17"/>
-      <c r="BP26" s="17"/>
-      <c r="BQ26" s="17"/>
-      <c r="BR26" s="17"/>
-      <c r="BS26" s="17"/>
-      <c r="BT26" s="18"/>
-      <c r="BU26" s="19"/>
-      <c r="BV26" s="17"/>
-      <c r="BW26" s="17"/>
-      <c r="BX26" s="18"/>
+      <c r="AX26" s="18"/>
+      <c r="AY26" s="19"/>
+      <c r="AZ26" s="20"/>
+      <c r="BA26" s="18"/>
+      <c r="BB26" s="18"/>
+      <c r="BC26" s="18"/>
+      <c r="BD26" s="18"/>
+      <c r="BE26" s="18"/>
+      <c r="BF26" s="19"/>
+      <c r="BG26" s="20"/>
+      <c r="BH26" s="18"/>
+      <c r="BI26" s="18"/>
+      <c r="BJ26" s="18"/>
+      <c r="BK26" s="18"/>
+      <c r="BL26" s="19"/>
+      <c r="BM26" s="20"/>
+      <c r="BN26" s="18"/>
+      <c r="BO26" s="18"/>
+      <c r="BP26" s="18"/>
+      <c r="BQ26" s="18"/>
+      <c r="BR26" s="18"/>
+      <c r="BS26" s="18"/>
+      <c r="BT26" s="19"/>
+      <c r="BU26" s="20"/>
+      <c r="BV26" s="18"/>
+      <c r="BW26" s="18"/>
+      <c r="BX26" s="19"/>
     </row>
     <row r="27">
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
-      <c r="AZ27" s="16" t="inlineStr">
+      <c r="AZ27" s="36" t="inlineStr">
         <is>
           <t>経営管理部長</t>
         </is>
       </c>
-      <c r="BA27" s="17"/>
-      <c r="BB27" s="17"/>
-      <c r="BC27" s="18"/>
-      <c r="BD27" s="19"/>
-      <c r="BE27" s="17"/>
-      <c r="BF27" s="17"/>
-      <c r="BG27" s="17"/>
-      <c r="BH27" s="17"/>
-      <c r="BI27" s="17"/>
-      <c r="BJ27" s="17"/>
-      <c r="BK27" s="25" t="inlineStr">
+      <c r="BA27" s="18"/>
+      <c r="BB27" s="18"/>
+      <c r="BC27" s="19"/>
+      <c r="BD27" s="20"/>
+      <c r="BE27" s="18"/>
+      <c r="BF27" s="18"/>
+      <c r="BG27" s="18"/>
+      <c r="BH27" s="18"/>
+      <c r="BI27" s="18"/>
+      <c r="BJ27" s="18"/>
+      <c r="BK27" s="37" t="inlineStr">
         <is>
           <t>検</t>
         </is>
       </c>
-      <c r="BL27" s="17"/>
-      <c r="BM27" s="17"/>
-      <c r="BN27" s="25" t="inlineStr">
+      <c r="BL27" s="18"/>
+      <c r="BM27" s="18"/>
+      <c r="BN27" s="37" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="BO27" s="17"/>
-      <c r="BP27" s="17"/>
-      <c r="BQ27" s="17"/>
-      <c r="BR27" s="17"/>
-      <c r="BS27" s="17"/>
-      <c r="BT27" s="18"/>
-      <c r="BV27" s="14" t="inlineStr">
+      <c r="BO27" s="18"/>
+      <c r="BP27" s="18"/>
+      <c r="BQ27" s="18"/>
+      <c r="BR27" s="18"/>
+      <c r="BS27" s="18"/>
+      <c r="BT27" s="19"/>
+      <c r="BV27" s="38" t="inlineStr">
         <is>
           <t>入力者</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>
@@ -1796,28 +1856,28 @@
       <c r="BX28" s="3"/>
     </row>
     <row r="29">
-      <c r="AZ29" s="24"/>
+      <c r="AZ29" s="27"/>
       <c r="BA29" s="6"/>
       <c r="BB29" s="6"/>
       <c r="BC29" s="7"/>
-      <c r="BD29" s="24"/>
+      <c r="BD29" s="27"/>
       <c r="BE29" s="6"/>
       <c r="BF29" s="6"/>
       <c r="BG29" s="6"/>
       <c r="BH29" s="7"/>
-      <c r="BI29" s="24"/>
+      <c r="BI29" s="27"/>
       <c r="BJ29" s="6"/>
       <c r="BK29" s="6"/>
       <c r="BL29" s="7"/>
-      <c r="BM29" s="24"/>
+      <c r="BM29" s="27"/>
       <c r="BN29" s="6"/>
       <c r="BO29" s="6"/>
       <c r="BP29" s="7"/>
-      <c r="BQ29" s="24"/>
+      <c r="BQ29" s="27"/>
       <c r="BR29" s="6"/>
       <c r="BS29" s="6"/>
       <c r="BT29" s="7"/>
-      <c r="BU29" s="24"/>
+      <c r="BU29" s="27"/>
       <c r="BV29" s="6"/>
       <c r="BW29" s="6"/>
       <c r="BX29" s="7"/>
@@ -1942,7 +2002,7 @@
       <c r="BH36" s="2"/>
       <c r="BI36" s="2"/>
       <c r="BJ36" s="2"/>
-      <c r="BK36" s="12" t="inlineStr">
+      <c r="BK36" s="13" t="inlineStr">
         <is>
           <t>－</t>
         </is>
@@ -1961,40 +2021,40 @@
       <c r="BW36" s="3"/>
     </row>
     <row r="37">
-      <c r="AZ37" s="13" t="inlineStr">
+      <c r="AZ37" s="14" t="inlineStr">
         <is>
           <t>住</t>
         </is>
       </c>
-      <c r="BF37" s="14" t="inlineStr">
+      <c r="BF37" s="15" t="inlineStr">
         <is>
           <t>所</t>
         </is>
       </c>
-      <c r="BW37" s="15"/>
+      <c r="BW37" s="16"/>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>支払票NO</t>
         </is>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="18"/>
-      <c r="AZ38" s="13" t="inlineStr">
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="19"/>
+      <c r="AZ38" s="14" t="inlineStr">
         <is>
           <t>取引先名</t>
         </is>
       </c>
-      <c r="BW38" s="15"/>
+      <c r="BW38" s="16"/>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
@@ -2002,17 +2062,17 @@
           <t>※請求書ご提出にあたってのお願い</t>
         </is>
       </c>
-      <c r="AZ39" s="13" t="inlineStr">
+      <c r="AZ39" s="14" t="inlineStr">
         <is>
           <t>代表者名</t>
         </is>
       </c>
-      <c r="BV39" s="14" t="inlineStr">
+      <c r="BV39" s="21" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="BW39" s="15"/>
+      <c r="BW39" s="16"/>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
@@ -2035,23 +2095,23 @@
           <t>太枠内と灰色の部分</t>
         </is>
       </c>
-      <c r="AZ40" s="20"/>
-      <c r="BG40" s="14" t="inlineStr">
+      <c r="AZ40" s="22"/>
+      <c r="BG40" s="9" t="inlineStr">
         <is>
           <t>電話FAX</t>
         </is>
       </c>
-      <c r="BM40" s="14" t="inlineStr">
+      <c r="BM40" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="BR40" s="14" t="inlineStr">
+      <c r="BR40" s="9" t="inlineStr">
         <is>
           <t>－－</t>
         </is>
       </c>
-      <c r="BW40" s="15"/>
+      <c r="BW40" s="16"/>
     </row>
     <row r="41">
       <c r="G41" s="9" t="inlineStr">
@@ -2064,12 +2124,12 @@
           <t>太枠内のみ</t>
         </is>
       </c>
-      <c r="AZ41" s="13" t="inlineStr">
+      <c r="AZ41" s="14" t="inlineStr">
         <is>
           <t>登録番号Ｔ</t>
         </is>
       </c>
-      <c r="BW41" s="15"/>
+      <c r="BW41" s="16"/>
     </row>
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
@@ -2077,7 +2137,7 @@
           <t>２．納入品目を記入しきれない場合は、総額を記入し御社の請求明細書を添付してください。</t>
         </is>
       </c>
-      <c r="AZ42" s="21" t="inlineStr">
+      <c r="AZ42" s="23" t="inlineStr">
         <is>
           <t>振込先情報</t>
         </is>
@@ -2091,7 +2151,7 @@
       <c r="BG42" s="6"/>
       <c r="BH42" s="6"/>
       <c r="BI42" s="6"/>
-      <c r="BJ42" s="22" t="inlineStr">
+      <c r="BJ42" s="24" t="inlineStr">
         <is>
           <t>銀行預金</t>
         </is>
@@ -2100,7 +2160,7 @@
       <c r="BL42" s="6"/>
       <c r="BM42" s="6"/>
       <c r="BN42" s="6"/>
-      <c r="BO42" s="22" t="inlineStr">
+      <c r="BO42" s="25" t="inlineStr">
         <is>
           <t>口座番号：支店</t>
         </is>
@@ -2115,7 +2175,7 @@
       <c r="BW42" s="7"/>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>３．軽油税、産廃税については、「工事名（品名）」欄に個別に明記してください。</t>
         </is>
@@ -2123,13 +2183,13 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="18"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="19"/>
       <c r="M43" s="1"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -2176,52 +2236,52 @@
       <c r="BD43" s="2"/>
       <c r="BE43" s="2"/>
       <c r="BF43" s="3"/>
-      <c r="BG43" s="16" t="inlineStr">
+      <c r="BG43" s="17" t="inlineStr">
         <is>
           <t>口座名義(ｶﾀｶﾅ)：</t>
         </is>
       </c>
-      <c r="BH43" s="17"/>
-      <c r="BI43" s="17"/>
-      <c r="BJ43" s="17"/>
-      <c r="BK43" s="17"/>
-      <c r="BL43" s="17"/>
-      <c r="BM43" s="17"/>
-      <c r="BN43" s="17"/>
-      <c r="BO43" s="17"/>
-      <c r="BP43" s="17"/>
-      <c r="BQ43" s="17"/>
-      <c r="BR43" s="17"/>
-      <c r="BS43" s="17"/>
-      <c r="BT43" s="18"/>
+      <c r="BH43" s="18"/>
+      <c r="BI43" s="18"/>
+      <c r="BJ43" s="18"/>
+      <c r="BK43" s="18"/>
+      <c r="BL43" s="18"/>
+      <c r="BM43" s="18"/>
+      <c r="BN43" s="18"/>
+      <c r="BO43" s="18"/>
+      <c r="BP43" s="18"/>
+      <c r="BQ43" s="18"/>
+      <c r="BR43" s="18"/>
+      <c r="BS43" s="18"/>
+      <c r="BT43" s="19"/>
       <c r="BU43" s="1"/>
       <c r="BV43" s="2"/>
       <c r="BW43" s="2"/>
       <c r="BX43" s="3"/>
     </row>
     <row r="44">
-      <c r="B44" s="24"/>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="B44" s="27"/>
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>工事NO</t>
         </is>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="7"/>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="29" t="inlineStr">
         <is>
           <t>科目コード</t>
         </is>
       </c>
-      <c r="M44" s="24"/>
-      <c r="N44" s="22" t="inlineStr">
+      <c r="M44" s="27"/>
+      <c r="N44" s="28" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="7"/>
-      <c r="Q44" s="24"/>
+      <c r="Q44" s="27"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
       <c r="T44" s="6"/>
@@ -2231,7 +2291,7 @@
       <c r="X44" s="6"/>
       <c r="Y44" s="6"/>
       <c r="Z44" s="6"/>
-      <c r="AA44" s="22" t="inlineStr">
+      <c r="AA44" s="28" t="inlineStr">
         <is>
           <t>工事名（品名）</t>
         </is>
@@ -2250,15 +2310,15 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
       <c r="AO44" s="7"/>
-      <c r="AP44" s="21" t="inlineStr">
+      <c r="AP44" s="30" t="inlineStr">
         <is>
           <t>内訳NO</t>
         </is>
       </c>
       <c r="AQ44" s="6"/>
       <c r="AR44" s="7"/>
-      <c r="AS44" s="24"/>
-      <c r="AT44" s="22" t="inlineStr">
+      <c r="AS44" s="27"/>
+      <c r="AT44" s="28" t="inlineStr">
         <is>
           <t>現在注文金額</t>
         </is>
@@ -2268,7 +2328,7 @@
       <c r="AW44" s="6"/>
       <c r="AX44" s="6"/>
       <c r="AY44" s="7"/>
-      <c r="AZ44" s="21" t="inlineStr">
+      <c r="AZ44" s="31" t="inlineStr">
         <is>
           <t>前回迄の支払額</t>
         </is>
@@ -2279,25 +2339,25 @@
       <c r="BD44" s="6"/>
       <c r="BE44" s="6"/>
       <c r="BF44" s="7"/>
-      <c r="BG44" s="19"/>
-      <c r="BH44" s="17"/>
-      <c r="BI44" s="17"/>
-      <c r="BJ44" s="17"/>
-      <c r="BK44" s="17"/>
-      <c r="BL44" s="25" t="inlineStr">
+      <c r="BG44" s="20"/>
+      <c r="BH44" s="18"/>
+      <c r="BI44" s="18"/>
+      <c r="BJ44" s="18"/>
+      <c r="BK44" s="18"/>
+      <c r="BL44" s="32" t="inlineStr">
         <is>
           <t>今回請求額</t>
         </is>
       </c>
-      <c r="BM44" s="17"/>
-      <c r="BN44" s="17"/>
-      <c r="BO44" s="17"/>
-      <c r="BP44" s="18"/>
-      <c r="BQ44" s="19"/>
-      <c r="BR44" s="17"/>
-      <c r="BS44" s="17"/>
-      <c r="BT44" s="18"/>
-      <c r="BU44" s="21" t="inlineStr">
+      <c r="BM44" s="18"/>
+      <c r="BN44" s="18"/>
+      <c r="BO44" s="18"/>
+      <c r="BP44" s="19"/>
+      <c r="BQ44" s="20"/>
+      <c r="BR44" s="18"/>
+      <c r="BS44" s="18"/>
+      <c r="BT44" s="19"/>
+      <c r="BU44" s="33" t="inlineStr">
         <is>
           <t>グリーン産業</t>
         </is>
@@ -2307,253 +2367,253 @@
       <c r="BX44" s="7"/>
     </row>
     <row r="45">
-      <c r="B45" s="19"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
-      <c r="AA45" s="17"/>
-      <c r="AB45" s="17"/>
-      <c r="AC45" s="17"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="17"/>
-      <c r="AF45" s="17"/>
-      <c r="AG45" s="17"/>
-      <c r="AH45" s="17"/>
-      <c r="AI45" s="17"/>
-      <c r="AJ45" s="17"/>
-      <c r="AK45" s="17"/>
-      <c r="AL45" s="17"/>
-      <c r="AM45" s="17"/>
-      <c r="AN45" s="17"/>
-      <c r="AO45" s="18"/>
-      <c r="AP45" s="19"/>
-      <c r="AQ45" s="17"/>
-      <c r="AR45" s="18"/>
-      <c r="AS45" s="19"/>
-      <c r="AT45" s="25" t="inlineStr">
+      <c r="B45" s="20"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="18"/>
+      <c r="AF45" s="18"/>
+      <c r="AG45" s="18"/>
+      <c r="AH45" s="18"/>
+      <c r="AI45" s="18"/>
+      <c r="AJ45" s="18"/>
+      <c r="AK45" s="18"/>
+      <c r="AL45" s="18"/>
+      <c r="AM45" s="18"/>
+      <c r="AN45" s="18"/>
+      <c r="AO45" s="19"/>
+      <c r="AP45" s="20"/>
+      <c r="AQ45" s="18"/>
+      <c r="AR45" s="19"/>
+      <c r="AS45" s="20"/>
+      <c r="AT45" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="AU45" s="17"/>
-      <c r="AV45" s="17"/>
-      <c r="AW45" s="17"/>
-      <c r="AX45" s="17"/>
-      <c r="AY45" s="18"/>
-      <c r="AZ45" s="19"/>
-      <c r="BA45" s="25" t="inlineStr">
+      <c r="AU45" s="18"/>
+      <c r="AV45" s="18"/>
+      <c r="AW45" s="18"/>
+      <c r="AX45" s="18"/>
+      <c r="AY45" s="19"/>
+      <c r="AZ45" s="20"/>
+      <c r="BA45" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BB45" s="17"/>
-      <c r="BC45" s="17"/>
-      <c r="BD45" s="17"/>
-      <c r="BE45" s="17"/>
-      <c r="BF45" s="18"/>
-      <c r="BG45" s="14" t="inlineStr">
+      <c r="BB45" s="18"/>
+      <c r="BC45" s="18"/>
+      <c r="BD45" s="18"/>
+      <c r="BE45" s="18"/>
+      <c r="BF45" s="19"/>
+      <c r="BG45" s="35" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BJ45" s="14" t="inlineStr">
+      <c r="BJ45" s="10" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BQ45" s="14" t="inlineStr">
+      <c r="BQ45" s="35" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="BR45" s="14" t="inlineStr">
+      <c r="BR45" s="10" t="inlineStr">
         <is>
           <t>税率</t>
         </is>
       </c>
-      <c r="BU45" s="19"/>
-      <c r="BV45" s="17"/>
-      <c r="BW45" s="17"/>
-      <c r="BX45" s="18"/>
+      <c r="BU45" s="20"/>
+      <c r="BV45" s="18"/>
+      <c r="BW45" s="18"/>
+      <c r="BX45" s="19"/>
     </row>
     <row r="46">
-      <c r="BG46" s="19"/>
-      <c r="BH46" s="17"/>
-      <c r="BI46" s="17"/>
-      <c r="BJ46" s="17"/>
-      <c r="BK46" s="17"/>
-      <c r="BL46" s="17"/>
-      <c r="BM46" s="17"/>
-      <c r="BN46" s="17"/>
-      <c r="BO46" s="17"/>
-      <c r="BP46" s="18"/>
-      <c r="BQ46" s="19"/>
-      <c r="BR46" s="17"/>
-      <c r="BS46" s="17"/>
-      <c r="BT46" s="18"/>
+      <c r="BG46" s="20"/>
+      <c r="BH46" s="18"/>
+      <c r="BI46" s="18"/>
+      <c r="BJ46" s="18"/>
+      <c r="BK46" s="18"/>
+      <c r="BL46" s="18"/>
+      <c r="BM46" s="18"/>
+      <c r="BN46" s="18"/>
+      <c r="BO46" s="18"/>
+      <c r="BP46" s="19"/>
+      <c r="BQ46" s="20"/>
+      <c r="BR46" s="18"/>
+      <c r="BS46" s="18"/>
+      <c r="BT46" s="19"/>
     </row>
     <row r="47">
-      <c r="B47" s="19"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="17"/>
-      <c r="AA47" s="17"/>
-      <c r="AB47" s="17"/>
-      <c r="AC47" s="17"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="17"/>
-      <c r="AF47" s="17"/>
-      <c r="AG47" s="17"/>
-      <c r="AH47" s="17"/>
-      <c r="AI47" s="17"/>
-      <c r="AJ47" s="17"/>
-      <c r="AK47" s="17"/>
-      <c r="AL47" s="17"/>
-      <c r="AM47" s="17"/>
-      <c r="AN47" s="17"/>
-      <c r="AO47" s="18"/>
-      <c r="AP47" s="19"/>
-      <c r="AQ47" s="17"/>
-      <c r="AR47" s="18"/>
-      <c r="AS47" s="19"/>
-      <c r="AT47" s="17"/>
-      <c r="AU47" s="17"/>
-      <c r="AV47" s="17"/>
-      <c r="AW47" s="17"/>
-      <c r="AX47" s="17"/>
-      <c r="AY47" s="18"/>
-      <c r="AZ47" s="19"/>
-      <c r="BA47" s="17"/>
-      <c r="BB47" s="17"/>
-      <c r="BC47" s="17"/>
-      <c r="BD47" s="17"/>
-      <c r="BE47" s="17"/>
-      <c r="BF47" s="18"/>
-      <c r="BU47" s="19"/>
-      <c r="BV47" s="17"/>
-      <c r="BW47" s="17"/>
-      <c r="BX47" s="18"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="18"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="18"/>
+      <c r="AE47" s="18"/>
+      <c r="AF47" s="18"/>
+      <c r="AG47" s="18"/>
+      <c r="AH47" s="18"/>
+      <c r="AI47" s="18"/>
+      <c r="AJ47" s="18"/>
+      <c r="AK47" s="18"/>
+      <c r="AL47" s="18"/>
+      <c r="AM47" s="18"/>
+      <c r="AN47" s="18"/>
+      <c r="AO47" s="19"/>
+      <c r="AP47" s="20"/>
+      <c r="AQ47" s="18"/>
+      <c r="AR47" s="19"/>
+      <c r="AS47" s="20"/>
+      <c r="AT47" s="18"/>
+      <c r="AU47" s="18"/>
+      <c r="AV47" s="18"/>
+      <c r="AW47" s="18"/>
+      <c r="AX47" s="18"/>
+      <c r="AY47" s="19"/>
+      <c r="AZ47" s="20"/>
+      <c r="BA47" s="18"/>
+      <c r="BB47" s="18"/>
+      <c r="BC47" s="18"/>
+      <c r="BD47" s="18"/>
+      <c r="BE47" s="18"/>
+      <c r="BF47" s="19"/>
+      <c r="BU47" s="20"/>
+      <c r="BV47" s="18"/>
+      <c r="BW47" s="18"/>
+      <c r="BX47" s="19"/>
     </row>
     <row r="48">
-      <c r="BG48" s="19"/>
-      <c r="BH48" s="17"/>
-      <c r="BI48" s="17"/>
-      <c r="BJ48" s="17"/>
-      <c r="BK48" s="17"/>
-      <c r="BL48" s="17"/>
-      <c r="BM48" s="17"/>
-      <c r="BN48" s="17"/>
-      <c r="BO48" s="17"/>
-      <c r="BP48" s="18"/>
-      <c r="BQ48" s="19"/>
-      <c r="BR48" s="17"/>
-      <c r="BS48" s="17"/>
-      <c r="BT48" s="18"/>
+      <c r="BG48" s="20"/>
+      <c r="BH48" s="18"/>
+      <c r="BI48" s="18"/>
+      <c r="BJ48" s="18"/>
+      <c r="BK48" s="18"/>
+      <c r="BL48" s="18"/>
+      <c r="BM48" s="18"/>
+      <c r="BN48" s="18"/>
+      <c r="BO48" s="18"/>
+      <c r="BP48" s="19"/>
+      <c r="BQ48" s="20"/>
+      <c r="BR48" s="18"/>
+      <c r="BS48" s="18"/>
+      <c r="BT48" s="19"/>
     </row>
     <row r="49">
-      <c r="B49" s="19"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="17"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="17"/>
-      <c r="AA49" s="17"/>
-      <c r="AB49" s="17"/>
-      <c r="AC49" s="17"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="17"/>
-      <c r="AF49" s="17"/>
-      <c r="AG49" s="17"/>
-      <c r="AH49" s="17"/>
-      <c r="AI49" s="17"/>
-      <c r="AJ49" s="17"/>
-      <c r="AK49" s="17"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49" s="17"/>
-      <c r="AN49" s="17"/>
-      <c r="AO49" s="18"/>
-      <c r="AP49" s="19"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49" s="18"/>
-      <c r="AS49" s="19"/>
-      <c r="AT49" s="17"/>
-      <c r="AU49" s="17"/>
-      <c r="AV49" s="17"/>
-      <c r="AW49" s="17"/>
-      <c r="AX49" s="17"/>
-      <c r="AY49" s="18"/>
-      <c r="AZ49" s="19"/>
-      <c r="BA49" s="17"/>
-      <c r="BB49" s="17"/>
-      <c r="BC49" s="17"/>
-      <c r="BD49" s="17"/>
-      <c r="BE49" s="17"/>
-      <c r="BF49" s="18"/>
-      <c r="BU49" s="19"/>
-      <c r="BV49" s="17"/>
-      <c r="BW49" s="17"/>
-      <c r="BX49" s="18"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="18"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="18"/>
+      <c r="Z49" s="18"/>
+      <c r="AA49" s="18"/>
+      <c r="AB49" s="18"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="18"/>
+      <c r="AE49" s="18"/>
+      <c r="AF49" s="18"/>
+      <c r="AG49" s="18"/>
+      <c r="AH49" s="18"/>
+      <c r="AI49" s="18"/>
+      <c r="AJ49" s="18"/>
+      <c r="AK49" s="18"/>
+      <c r="AL49" s="18"/>
+      <c r="AM49" s="18"/>
+      <c r="AN49" s="18"/>
+      <c r="AO49" s="19"/>
+      <c r="AP49" s="20"/>
+      <c r="AQ49" s="18"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="20"/>
+      <c r="AT49" s="18"/>
+      <c r="AU49" s="18"/>
+      <c r="AV49" s="18"/>
+      <c r="AW49" s="18"/>
+      <c r="AX49" s="18"/>
+      <c r="AY49" s="19"/>
+      <c r="AZ49" s="20"/>
+      <c r="BA49" s="18"/>
+      <c r="BB49" s="18"/>
+      <c r="BC49" s="18"/>
+      <c r="BD49" s="18"/>
+      <c r="BE49" s="18"/>
+      <c r="BF49" s="19"/>
+      <c r="BU49" s="20"/>
+      <c r="BV49" s="18"/>
+      <c r="BW49" s="18"/>
+      <c r="BX49" s="19"/>
     </row>
     <row r="50">
       <c r="B50" s="1"/>
@@ -2626,22 +2686,22 @@
       <c r="BX50" s="3"/>
     </row>
     <row r="51">
-      <c r="B51" s="24"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="7"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="24"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="27"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="P51" s="7"/>
-      <c r="Q51" s="24"/>
+      <c r="Q51" s="27"/>
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
       <c r="T51" s="6"/>
@@ -2666,24 +2726,24 @@
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
       <c r="AO51" s="7"/>
-      <c r="AP51" s="24"/>
+      <c r="AP51" s="27"/>
       <c r="AQ51" s="6"/>
       <c r="AR51" s="7"/>
-      <c r="AS51" s="24"/>
+      <c r="AS51" s="27"/>
       <c r="AT51" s="6"/>
       <c r="AU51" s="6"/>
       <c r="AV51" s="6"/>
       <c r="AW51" s="6"/>
       <c r="AX51" s="6"/>
       <c r="AY51" s="7"/>
-      <c r="AZ51" s="24"/>
+      <c r="AZ51" s="27"/>
       <c r="BA51" s="6"/>
       <c r="BB51" s="6"/>
       <c r="BC51" s="6"/>
       <c r="BD51" s="6"/>
       <c r="BE51" s="6"/>
       <c r="BF51" s="7"/>
-      <c r="BG51" s="24"/>
+      <c r="BG51" s="27"/>
       <c r="BH51" s="6"/>
       <c r="BI51" s="6"/>
       <c r="BJ51" s="6"/>
@@ -2693,294 +2753,294 @@
       <c r="BN51" s="6"/>
       <c r="BO51" s="6"/>
       <c r="BP51" s="7"/>
-      <c r="BQ51" s="24"/>
+      <c r="BQ51" s="27"/>
       <c r="BR51" s="6"/>
       <c r="BS51" s="6"/>
       <c r="BT51" s="7"/>
-      <c r="BU51" s="24"/>
+      <c r="BU51" s="27"/>
       <c r="BV51" s="6"/>
       <c r="BW51" s="6"/>
       <c r="BX51" s="7"/>
     </row>
     <row r="52">
-      <c r="B52" s="19"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
-      <c r="Z52" s="17"/>
-      <c r="AA52" s="17"/>
-      <c r="AB52" s="17"/>
-      <c r="AC52" s="17"/>
-      <c r="AD52" s="17"/>
-      <c r="AE52" s="17"/>
-      <c r="AF52" s="17"/>
-      <c r="AG52" s="17"/>
-      <c r="AH52" s="17"/>
-      <c r="AI52" s="17"/>
-      <c r="AJ52" s="17"/>
-      <c r="AK52" s="17"/>
-      <c r="AL52" s="17"/>
-      <c r="AM52" s="17"/>
-      <c r="AN52" s="17"/>
-      <c r="AO52" s="17"/>
-      <c r="AP52" s="17"/>
-      <c r="AQ52" s="17"/>
-      <c r="AR52" s="17"/>
-      <c r="AS52" s="17"/>
-      <c r="AT52" s="17"/>
-      <c r="AU52" s="17"/>
-      <c r="AV52" s="17"/>
-      <c r="AW52" s="17"/>
-      <c r="AX52" s="17"/>
-      <c r="AY52" s="18"/>
-      <c r="AZ52" s="19"/>
-      <c r="BA52" s="25" t="inlineStr">
+      <c r="B52" s="20"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="18"/>
+      <c r="Z52" s="18"/>
+      <c r="AA52" s="18"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="18"/>
+      <c r="AF52" s="18"/>
+      <c r="AG52" s="18"/>
+      <c r="AH52" s="18"/>
+      <c r="AI52" s="18"/>
+      <c r="AJ52" s="18"/>
+      <c r="AK52" s="18"/>
+      <c r="AL52" s="18"/>
+      <c r="AM52" s="18"/>
+      <c r="AN52" s="18"/>
+      <c r="AO52" s="18"/>
+      <c r="AP52" s="18"/>
+      <c r="AQ52" s="18"/>
+      <c r="AR52" s="18"/>
+      <c r="AS52" s="18"/>
+      <c r="AT52" s="18"/>
+      <c r="AU52" s="18"/>
+      <c r="AV52" s="18"/>
+      <c r="AW52" s="18"/>
+      <c r="AX52" s="18"/>
+      <c r="AY52" s="19"/>
+      <c r="AZ52" s="20"/>
+      <c r="BA52" s="34" t="inlineStr">
         <is>
           <t>（税抜金額）</t>
         </is>
       </c>
-      <c r="BB52" s="17"/>
-      <c r="BC52" s="17"/>
-      <c r="BD52" s="17"/>
-      <c r="BE52" s="17"/>
-      <c r="BF52" s="18"/>
-      <c r="BG52" s="19"/>
-      <c r="BH52" s="25" t="inlineStr">
+      <c r="BB52" s="18"/>
+      <c r="BC52" s="18"/>
+      <c r="BD52" s="18"/>
+      <c r="BE52" s="18"/>
+      <c r="BF52" s="19"/>
+      <c r="BG52" s="20"/>
+      <c r="BH52" s="34" t="inlineStr">
         <is>
           <t>(消費税)</t>
         </is>
       </c>
-      <c r="BI52" s="17"/>
-      <c r="BJ52" s="17"/>
-      <c r="BK52" s="17"/>
-      <c r="BL52" s="18"/>
-      <c r="BM52" s="19"/>
-      <c r="BN52" s="17"/>
-      <c r="BO52" s="25" t="inlineStr">
+      <c r="BI52" s="18"/>
+      <c r="BJ52" s="18"/>
+      <c r="BK52" s="18"/>
+      <c r="BL52" s="19"/>
+      <c r="BM52" s="20"/>
+      <c r="BN52" s="18"/>
+      <c r="BO52" s="34" t="inlineStr">
         <is>
           <t>(税込金額)</t>
         </is>
       </c>
-      <c r="BP52" s="17"/>
-      <c r="BQ52" s="17"/>
-      <c r="BR52" s="17"/>
-      <c r="BS52" s="17"/>
-      <c r="BT52" s="18"/>
-      <c r="BU52" s="19"/>
-      <c r="BV52" s="17"/>
-      <c r="BW52" s="17"/>
-      <c r="BX52" s="18"/>
+      <c r="BP52" s="18"/>
+      <c r="BQ52" s="18"/>
+      <c r="BR52" s="18"/>
+      <c r="BS52" s="18"/>
+      <c r="BT52" s="19"/>
+      <c r="BU52" s="20"/>
+      <c r="BV52" s="18"/>
+      <c r="BW52" s="18"/>
+      <c r="BX52" s="19"/>
     </row>
     <row r="53">
-      <c r="AR53" s="14" t="inlineStr">
+      <c r="AR53" s="10" t="inlineStr">
         <is>
           <t>非・不課税小計</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="19"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
-      <c r="Z54" s="17"/>
-      <c r="AA54" s="17"/>
-      <c r="AB54" s="17"/>
-      <c r="AC54" s="17"/>
-      <c r="AD54" s="17"/>
-      <c r="AE54" s="17"/>
-      <c r="AF54" s="17"/>
-      <c r="AG54" s="17"/>
-      <c r="AH54" s="17"/>
-      <c r="AI54" s="17"/>
-      <c r="AJ54" s="17"/>
-      <c r="AK54" s="17"/>
-      <c r="AL54" s="17"/>
-      <c r="AM54" s="17"/>
-      <c r="AN54" s="17"/>
-      <c r="AO54" s="17"/>
-      <c r="AP54" s="17"/>
-      <c r="AQ54" s="17"/>
-      <c r="AR54" s="17"/>
-      <c r="AS54" s="17"/>
-      <c r="AT54" s="17"/>
-      <c r="AU54" s="17"/>
-      <c r="AV54" s="25" t="inlineStr">
+      <c r="B54" s="20"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="18"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="AD54" s="18"/>
+      <c r="AE54" s="18"/>
+      <c r="AF54" s="18"/>
+      <c r="AG54" s="18"/>
+      <c r="AH54" s="18"/>
+      <c r="AI54" s="18"/>
+      <c r="AJ54" s="18"/>
+      <c r="AK54" s="18"/>
+      <c r="AL54" s="18"/>
+      <c r="AM54" s="18"/>
+      <c r="AN54" s="18"/>
+      <c r="AO54" s="18"/>
+      <c r="AP54" s="18"/>
+      <c r="AQ54" s="18"/>
+      <c r="AR54" s="18"/>
+      <c r="AS54" s="18"/>
+      <c r="AT54" s="18"/>
+      <c r="AU54" s="18"/>
+      <c r="AV54" s="34" t="inlineStr">
         <is>
           <t>8%小計</t>
         </is>
       </c>
-      <c r="AW54" s="17"/>
-      <c r="AX54" s="17"/>
-      <c r="AY54" s="18"/>
-      <c r="AZ54" s="19"/>
-      <c r="BA54" s="17"/>
-      <c r="BB54" s="17"/>
-      <c r="BC54" s="17"/>
-      <c r="BD54" s="17"/>
-      <c r="BE54" s="17"/>
-      <c r="BF54" s="18"/>
-      <c r="BG54" s="19"/>
-      <c r="BH54" s="17"/>
-      <c r="BI54" s="17"/>
-      <c r="BJ54" s="17"/>
-      <c r="BK54" s="17"/>
-      <c r="BL54" s="18"/>
-      <c r="BM54" s="19"/>
-      <c r="BN54" s="17"/>
-      <c r="BO54" s="17"/>
-      <c r="BP54" s="17"/>
-      <c r="BQ54" s="17"/>
-      <c r="BR54" s="17"/>
-      <c r="BS54" s="17"/>
-      <c r="BT54" s="18"/>
-      <c r="BU54" s="19"/>
-      <c r="BV54" s="17"/>
-      <c r="BW54" s="17"/>
-      <c r="BX54" s="18"/>
+      <c r="AW54" s="18"/>
+      <c r="AX54" s="18"/>
+      <c r="AY54" s="19"/>
+      <c r="AZ54" s="20"/>
+      <c r="BA54" s="18"/>
+      <c r="BB54" s="18"/>
+      <c r="BC54" s="18"/>
+      <c r="BD54" s="18"/>
+      <c r="BE54" s="18"/>
+      <c r="BF54" s="19"/>
+      <c r="BG54" s="20"/>
+      <c r="BH54" s="18"/>
+      <c r="BI54" s="18"/>
+      <c r="BJ54" s="18"/>
+      <c r="BK54" s="18"/>
+      <c r="BL54" s="19"/>
+      <c r="BM54" s="20"/>
+      <c r="BN54" s="18"/>
+      <c r="BO54" s="18"/>
+      <c r="BP54" s="18"/>
+      <c r="BQ54" s="18"/>
+      <c r="BR54" s="18"/>
+      <c r="BS54" s="18"/>
+      <c r="BT54" s="19"/>
+      <c r="BU54" s="20"/>
+      <c r="BV54" s="18"/>
+      <c r="BW54" s="18"/>
+      <c r="BX54" s="19"/>
     </row>
     <row r="55">
-      <c r="AU55" s="14" t="inlineStr">
+      <c r="AU55" s="10" t="inlineStr">
         <is>
           <t>10%小計</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="19"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="17"/>
-      <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
-      <c r="X56" s="17"/>
-      <c r="Y56" s="17"/>
-      <c r="Z56" s="17"/>
-      <c r="AA56" s="17"/>
-      <c r="AB56" s="17"/>
-      <c r="AC56" s="17"/>
-      <c r="AD56" s="17"/>
-      <c r="AE56" s="17"/>
-      <c r="AF56" s="17"/>
-      <c r="AG56" s="17"/>
-      <c r="AH56" s="17"/>
-      <c r="AI56" s="17"/>
-      <c r="AJ56" s="17"/>
-      <c r="AK56" s="17"/>
-      <c r="AL56" s="17"/>
-      <c r="AM56" s="17"/>
-      <c r="AN56" s="17"/>
-      <c r="AO56" s="17"/>
-      <c r="AP56" s="17"/>
-      <c r="AQ56" s="17"/>
-      <c r="AR56" s="17"/>
-      <c r="AS56" s="17"/>
-      <c r="AT56" s="17"/>
-      <c r="AU56" s="17"/>
-      <c r="AV56" s="17"/>
-      <c r="AW56" s="25" t="inlineStr">
+      <c r="B56" s="20"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="18"/>
+      <c r="X56" s="18"/>
+      <c r="Y56" s="18"/>
+      <c r="Z56" s="18"/>
+      <c r="AA56" s="18"/>
+      <c r="AB56" s="18"/>
+      <c r="AC56" s="18"/>
+      <c r="AD56" s="18"/>
+      <c r="AE56" s="18"/>
+      <c r="AF56" s="18"/>
+      <c r="AG56" s="18"/>
+      <c r="AH56" s="18"/>
+      <c r="AI56" s="18"/>
+      <c r="AJ56" s="18"/>
+      <c r="AK56" s="18"/>
+      <c r="AL56" s="18"/>
+      <c r="AM56" s="18"/>
+      <c r="AN56" s="18"/>
+      <c r="AO56" s="18"/>
+      <c r="AP56" s="18"/>
+      <c r="AQ56" s="18"/>
+      <c r="AR56" s="18"/>
+      <c r="AS56" s="18"/>
+      <c r="AT56" s="18"/>
+      <c r="AU56" s="18"/>
+      <c r="AV56" s="18"/>
+      <c r="AW56" s="34" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="AX56" s="17"/>
-      <c r="AY56" s="18"/>
-      <c r="AZ56" s="19"/>
-      <c r="BA56" s="17"/>
-      <c r="BB56" s="17"/>
-      <c r="BC56" s="17"/>
-      <c r="BD56" s="17"/>
-      <c r="BE56" s="17"/>
-      <c r="BF56" s="18"/>
-      <c r="BG56" s="19"/>
-      <c r="BH56" s="17"/>
-      <c r="BI56" s="17"/>
-      <c r="BJ56" s="17"/>
-      <c r="BK56" s="17"/>
-      <c r="BL56" s="18"/>
-      <c r="BM56" s="19"/>
-      <c r="BN56" s="17"/>
-      <c r="BO56" s="17"/>
-      <c r="BP56" s="17"/>
-      <c r="BQ56" s="17"/>
-      <c r="BR56" s="17"/>
-      <c r="BS56" s="17"/>
-      <c r="BT56" s="18"/>
-      <c r="BU56" s="19"/>
-      <c r="BV56" s="17"/>
-      <c r="BW56" s="17"/>
-      <c r="BX56" s="18"/>
+      <c r="AX56" s="18"/>
+      <c r="AY56" s="19"/>
+      <c r="AZ56" s="20"/>
+      <c r="BA56" s="18"/>
+      <c r="BB56" s="18"/>
+      <c r="BC56" s="18"/>
+      <c r="BD56" s="18"/>
+      <c r="BE56" s="18"/>
+      <c r="BF56" s="19"/>
+      <c r="BG56" s="20"/>
+      <c r="BH56" s="18"/>
+      <c r="BI56" s="18"/>
+      <c r="BJ56" s="18"/>
+      <c r="BK56" s="18"/>
+      <c r="BL56" s="19"/>
+      <c r="BM56" s="20"/>
+      <c r="BN56" s="18"/>
+      <c r="BO56" s="18"/>
+      <c r="BP56" s="18"/>
+      <c r="BQ56" s="18"/>
+      <c r="BR56" s="18"/>
+      <c r="BS56" s="18"/>
+      <c r="BT56" s="19"/>
+      <c r="BU56" s="20"/>
+      <c r="BV56" s="18"/>
+      <c r="BW56" s="18"/>
+      <c r="BX56" s="19"/>
     </row>
     <row r="57">
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>※提出部数</t>
         </is>
       </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="H57" s="15" t="inlineStr">
         <is>
           <t>1部（白黒で構いません）・・・毎月５日必着</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>※毎年１２月のみ２０日締切（２５日必着）翌月末日支払いとさせていただきます。</t>
         </is>
